--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79000</v>
+        <v>79001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>79863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79000</v>
+        <v>79001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79833</v>
+        <v>79834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79000</v>
+        <v>79001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79863</v>
+        <v>79864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79834</v>
+        <v>79835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79864</v>
+        <v>79865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79865</v>
+        <v>79867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131106808</v>
       </c>
       <c r="B3" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131106807</v>
       </c>
       <c r="B4" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>131106804</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>131106805</v>
       </c>
       <c r="B6" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>131106806</v>
       </c>
       <c r="B7" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>131106803</v>
       </c>
       <c r="B8" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117863964</v>
+        <v>131106804</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600298</v>
+        <v>600308</v>
       </c>
       <c r="R2" t="n">
-        <v>6972918</v>
+        <v>6972996</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,14 +738,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2025_0372</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131106808</v>
+        <v>117863964</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,26 +819,17 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600356</v>
+        <v>600298</v>
       </c>
       <c r="R3" t="n">
-        <v>6973038</v>
+        <v>6972918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,29 +854,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2025_0368</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:39</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,26 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106807</v>
+        <v>131106803</v>
       </c>
       <c r="B4" t="n">
-        <v>79873</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +899,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600345</v>
+        <v>600279</v>
       </c>
       <c r="R4" t="n">
-        <v>6973042</v>
+        <v>6972994</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +962,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025_0369</t>
+          <t>2025_0373</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -986,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106804</v>
+        <v>131106805</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,34 +1024,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600308</v>
+        <v>600334</v>
       </c>
       <c r="R5" t="n">
-        <v>6972996</v>
+        <v>6973001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1087,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0372</t>
+          <t>2025_0371</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1102,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106805</v>
+        <v>131106808</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600334</v>
+        <v>600356</v>
       </c>
       <c r="R6" t="n">
-        <v>6973001</v>
+        <v>6973038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1212,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0371</t>
+          <t>2025_0368</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106806</v>
+        <v>131106807</v>
       </c>
       <c r="B7" t="n">
-        <v>79844</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1303,7 +1298,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600353</v>
+        <v>600345</v>
       </c>
       <c r="R7" t="n">
-        <v>6973046</v>
+        <v>6973042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1337,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0370</t>
+          <t>2025_0369</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1352,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106803</v>
+        <v>131106806</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,31 +1399,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600279</v>
+        <v>600353</v>
       </c>
       <c r="R8" t="n">
-        <v>6972994</v>
+        <v>6973046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0373</t>
+          <t>2025_0370</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1477,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131106804</v>
+        <v>135342343</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600308</v>
+        <v>600216</v>
       </c>
       <c r="R2" t="n">
-        <v>6972996</v>
+        <v>6972924</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,29 +741,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2025_0372</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,61 +773,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117863964</v>
+        <v>131106804</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600298</v>
+        <v>600308</v>
       </c>
       <c r="R3" t="n">
-        <v>6972918</v>
+        <v>6972996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,14 +848,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025_0372</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,19 +885,23 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106803</v>
+        <v>117863964</v>
       </c>
       <c r="B4" t="n">
         <v>79084</v>
@@ -916,26 +929,17 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600279</v>
+        <v>600298</v>
       </c>
       <c r="R4" t="n">
-        <v>6972994</v>
+        <v>6972918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,29 +964,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2025_0373</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,23 +986,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106805</v>
+        <v>131106803</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1048,7 +1033,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600334</v>
+        <v>600279</v>
       </c>
       <c r="R5" t="n">
-        <v>6973001</v>
+        <v>6972994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1072,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0371</t>
+          <t>2025_0373</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1097,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106808</v>
+        <v>131106805</v>
       </c>
       <c r="B6" t="n">
         <v>79084</v>
@@ -1182,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600356</v>
+        <v>600334</v>
       </c>
       <c r="R6" t="n">
-        <v>6973038</v>
+        <v>6973001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1197,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0368</t>
+          <t>2025_0371</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1222,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106807</v>
+        <v>131106808</v>
       </c>
       <c r="B7" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,26 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600345</v>
+        <v>600356</v>
       </c>
       <c r="R7" t="n">
-        <v>6973042</v>
+        <v>6973038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1322,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0369</t>
+          <t>2025_0368</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1347,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106806</v>
+        <v>135342344</v>
       </c>
       <c r="B8" t="n">
-        <v>79917</v>
+        <v>79130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,46 +1384,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600353</v>
+        <v>600280</v>
       </c>
       <c r="R8" t="n">
-        <v>6973046</v>
+        <v>6973063</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,29 +1439,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2025_0370</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,15 +1471,481 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135342345</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordansjön, Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600215</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972928</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131106807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6973042</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2025_0369</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135342346</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nordansjön, Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>600360</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6973010</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131106806</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600353</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6973046</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2025_0370</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342343</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106804</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117863964</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106803</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106805</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106808</t>
         </is>
       </c>
     </row>
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342344</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342345</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1713,6 +1758,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106807</t>
         </is>
       </c>
     </row>
@@ -1825,6 +1875,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342346</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1950,8 +2005,26 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135342343</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>135342344</v>
       </c>
       <c r="B8" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>135342345</v>
       </c>
       <c r="B9" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>135342346</v>
       </c>
       <c r="B11" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135342343</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>135342344</v>
       </c>
       <c r="B8" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>135342345</v>
       </c>
       <c r="B9" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>135342346</v>
       </c>
       <c r="B11" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 24016-2025 artfynd.xlsx
+++ b/artfynd/A 24016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131106804</v>
+        <v>135342343</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600308</v>
+        <v>600216</v>
       </c>
       <c r="R2" t="n">
-        <v>6972996</v>
+        <v>6972924</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +746,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2025_0372</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,66 +778,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106804</t>
+          <t>https://artportalen.se/Sighting/135342343</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117863964</v>
+        <v>131106804</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Boda, Mpd</t>
+          <t>Paljack, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600298</v>
+        <v>600308</v>
       </c>
       <c r="R3" t="n">
-        <v>6972918</v>
+        <v>6972996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,14 +858,29 @@
           <t>Liden</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025_0372</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,24 +895,28 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117863964</t>
+          <t>https://artportalen.se/Sighting/131106804</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131106803</v>
+        <v>117863964</v>
       </c>
       <c r="B4" t="n">
         <v>79084</v>
@@ -931,26 +944,17 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Boda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600279</v>
+        <v>600298</v>
       </c>
       <c r="R4" t="n">
-        <v>6972994</v>
+        <v>6972918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,29 +979,14 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2025_0373</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,28 +1001,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106803</t>
+          <t>https://artportalen.se/Sighting/117863964</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131106805</v>
+        <v>131106803</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1068,7 +1053,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1077,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600334</v>
+        <v>600279</v>
       </c>
       <c r="R5" t="n">
-        <v>6973001</v>
+        <v>6972994</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1092,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025_0371</t>
+          <t>2025_0373</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1117,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,13 +1142,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106805</t>
+          <t>https://artportalen.se/Sighting/131106803</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131106808</v>
+        <v>131106805</v>
       </c>
       <c r="B6" t="n">
         <v>79084</v>
@@ -1207,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600356</v>
+        <v>600334</v>
       </c>
       <c r="R6" t="n">
-        <v>6973038</v>
+        <v>6973001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1222,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025_0368</t>
+          <t>2025_0371</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1247,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,16 +1272,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106808</t>
+          <t>https://artportalen.se/Sighting/131106805</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131106807</v>
+        <v>131106808</v>
       </c>
       <c r="B7" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,26 +1289,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1337,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600345</v>
+        <v>600356</v>
       </c>
       <c r="R7" t="n">
-        <v>6973042</v>
+        <v>6973038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1352,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025_0369</t>
+          <t>2025_0368</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1377,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1387,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,16 +1402,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106807</t>
+          <t>https://artportalen.se/Sighting/131106808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106806</v>
+        <v>135342344</v>
       </c>
       <c r="B8" t="n">
-        <v>79917</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,46 +1419,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Paljack, Mpd</t>
+          <t>Nordansjön, Nordansjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600353</v>
+        <v>600280</v>
       </c>
       <c r="R8" t="n">
-        <v>6973046</v>
+        <v>6973063</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,29 +1474,24 @@
           <t>Liden</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2025_0370</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,20 +1506,506 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342344</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135342345</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordansjön, Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600215</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972928</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342345</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131106807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6973042</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2025_0369</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106807</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135342346</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nordansjön, Nordansjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>600360</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6973010</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135342346</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131106806</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Paljack, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600353</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6973046</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2025_0370</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131106806</t>
         </is>
@@ -1560,6 +2020,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
